--- a/lib/Offer Letter Comparison - Visit Type Points Matrix - for John.xlsx
+++ b/lib/Offer Letter Comparison - Visit Type Points Matrix - for John.xlsx
@@ -5,16 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acaciahomehealth-my.sharepoint.com/personal/stephanie_jacobs_acaciahealth_net/Documents/Documents/Payroll/Points Reports/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JohnEricta\Documents\Scripts\JS\pointsReport\lib\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{4A499BBA-3430-4F3F-8B56-3BD09EC7E9F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F38E69BA-F0A1-4226-80B3-BC934A5CB543}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09EF4F53-77F0-4049-8ADE-1BBFEE08461A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Visit Type Points" sheetId="1" r:id="rId1"/>
-    <sheet name="Offer Letter Terms" sheetId="2" r:id="rId2"/>
+    <sheet name="Offer Letter Terms" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -1150,7 +1150,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E5442C6-23EC-46EA-8401-B22914C5037B}">
   <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
